--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Income Optimizer Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Income Optimizer Fund (FOF).xlsx
@@ -14,15 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
   <si>
-    <t>ICICI Prudential Income Optimizer Fund (FOF)</t>
-  </si>
-  <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>ICICI Prudential Income Plus Arbitrage Active FOF</t>
+  </si>
+  <si>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -55,31 +55,25 @@
     <t/>
   </si>
   <si>
-    <t>ICICI Prudential Short Term Fund - Direct Plan -  Growth Option</t>
-  </si>
-  <si>
-    <t>INF109K013N3</t>
+    <t>ICICI Prudential Corporate Bond Fund- Direct Plan -  Growth</t>
+  </si>
+  <si>
+    <t>INF109K016B1</t>
   </si>
   <si>
     <t>Capital Markets</t>
   </si>
   <si>
-    <t>ICICI Prudential Equity Savings Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109KA11J9</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Equity Minimum Variance Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC10Y6</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Exports and Services Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109K01W25</t>
+    <t>ICICI Prudential Equity Arbitrage Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109K016O4</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Long Term Bond Fund - DIRECT - GROWTH</t>
+  </si>
+  <si>
+    <t>INF109K017L8</t>
   </si>
   <si>
     <t>TREPS</t>
@@ -97,7 +91,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -109,7 +103,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - NIFTY 50 TRI (35%) + CRISIL Composite Bond Index (65%)</t>
+    <t>Benchmark name - NIFTY 50 TRI (35%) + CRISIL Composite Bond Fund Index (65%)</t>
   </si>
 </sst>
 </file>
@@ -412,13 +406,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -436,8 +430,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="5219700"/>
-          <a:ext cx="4467225" cy="1905000"/>
+          <a:off x="666750" y="5029200"/>
+          <a:ext cx="4133850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -451,13 +445,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -475,8 +469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="8077200"/>
-          <a:ext cx="4467225" cy="1905000"/>
+          <a:off x="666750" y="7886700"/>
+          <a:ext cx="4133850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -809,12 +803,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J39"/>
+  <dimension ref="B1:J38"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="67.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.714285714285715" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="62.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="19.571428571428573" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
@@ -903,10 +897,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>26127.27</v>
+        <v>53247.49</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9754801702012</v>
+        <v>0.896383700338</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -926,13 +920,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>24284436.776</v>
+        <v>98482684.992</v>
       </c>
       <c r="F6" s="15">
-        <v>15292.95</v>
+        <v>30777.41</v>
       </c>
       <c r="G6" s="16">
-        <v>0.5709731429606</v>
+        <v>0.5181158522706</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -952,13 +946,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>34253955.849</v>
+        <v>58404897.86</v>
       </c>
       <c r="F7" s="15">
-        <v>7957.19</v>
+        <v>21358.55</v>
       </c>
       <c r="G7" s="16">
-        <v>0.2970873365462</v>
+        <v>0.3595560294552</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -978,13 +972,13 @@
         <v>15</v>
       </c>
       <c r="E8" s="14">
-        <v>15227665.013</v>
+        <v>1114886.714</v>
       </c>
       <c r="F8" s="15">
-        <v>1501.45</v>
+        <v>1111.53</v>
       </c>
       <c r="G8" s="16">
-        <v>0.056057701457</v>
+        <v>0.0187118186122</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -995,157 +989,131 @@
     </row>
     <row r="9" spans="2:9" ht="15" customHeight="1">
       <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15" customHeight="1">
+      <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9">
+        <v>6326.72</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.1065058406434</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="15" customHeight="1">
+      <c r="B11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15" customHeight="1">
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="14">
-        <v>835519.977</v>
-      </c>
-      <c r="F9" s="15">
-        <v>1375.68</v>
-      </c>
-      <c r="G9" s="16">
-        <v>0.0513619892374</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="15" customHeight="1">
-      <c r="B10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="15" customHeight="1">
-      <c r="B11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="9">
-        <v>693.29</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0.025884474237</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="15" customHeight="1">
-      <c r="B12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="C12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="18">
+        <v>-171.6461426800015</v>
+      </c>
+      <c r="G12" s="19">
+        <v>-0.002889540981636436</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="15" customHeight="1">
       <c r="B13" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="18">
+        <v>59402.56385732</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.9999999999997635</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="18">
-        <v>-36.55064940000011</v>
-      </c>
-      <c r="G13" s="19">
-        <v>-0.0013646444384616122</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="15" customHeight="1">
-      <c r="B14" s="17" t="s">
+    </row>
+    <row r="17" ht="27.5" customHeight="1">
+      <c r="B17" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="18">
-        <v>26784.0093506</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0.9999999999997383</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="18" ht="27.5" customHeight="1">
       <c r="B18" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="27.5" customHeight="1">
       <c r="B19" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" ht="15">
+      <c r="B22" s="21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" ht="27.5" customHeight="1">
-      <c r="B20" s="20" t="s">
+    <row r="37" ht="15">
+      <c r="B37" s="21" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="15">
-      <c r="B23" s="21" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="38" ht="15">
       <c r="B38" s="21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" ht="15">
-      <c r="B39" s="21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1153,10 +1121,10 @@
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
